--- a/data/trans_dic/IP24_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que no hacen ejercicio</t>
+          <t>Menores que no hacen ejercicio (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,46; 30,7</t>
+          <t>11,77; 29,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,39; 37,23</t>
+          <t>17,01; 36,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,72; 22,97</t>
+          <t>9,36; 24,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59,34; 78,93</t>
+          <t>58,96; 79,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,2; 31,94</t>
+          <t>14,37; 32,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,2; 31,33</t>
+          <t>14,69; 32,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,53; 23,89</t>
+          <t>8,65; 24,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>58,88; 78,48</t>
+          <t>59,02; 77,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,17; 27,08</t>
+          <t>15,1; 27,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,36; 32,35</t>
+          <t>17,46; 31,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 21,18</t>
+          <t>9,75; 21,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>61,63; 75,45</t>
+          <t>61,38; 75,02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,54; 28,49</t>
+          <t>16,02; 29,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,53; 26,39</t>
+          <t>13,61; 25,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,62; 31,42</t>
+          <t>18,14; 30,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,28; 70,83</t>
+          <t>16,16; 65,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,51; 18,2</t>
+          <t>8,36; 19,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,62; 24,54</t>
+          <t>11,68; 23,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,9; 21,9</t>
+          <t>11,45; 22,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,31; 20,23</t>
+          <t>8,5; 19,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,7; 21,56</t>
+          <t>13,69; 21,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,07; 22,59</t>
+          <t>14,17; 23,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,71; 24,96</t>
+          <t>16,06; 24,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,15; 50,55</t>
+          <t>14,15; 48,77</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,13; 41,83</t>
+          <t>22,17; 40,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,93; 24,72</t>
+          <t>10,62; 25,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,13; 34,34</t>
+          <t>16,47; 34,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,09; 19,34</t>
+          <t>6,03; 19,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,21; 29,28</t>
+          <t>14,13; 28,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,51; 23,19</t>
+          <t>9,59; 23,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,56; 26,18</t>
+          <t>11,69; 26,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 17,9</t>
+          <t>6,19; 17,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,12; 32,06</t>
+          <t>19,09; 31,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,57; 22,09</t>
+          <t>11,18; 21,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,12; 27,35</t>
+          <t>15,87; 27,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,34; 16,5</t>
+          <t>7,49; 15,95</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,64; 26,81</t>
+          <t>12,51; 27,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,35; 21,19</t>
+          <t>8,46; 20,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,54; 37,19</t>
+          <t>19,94; 37,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,04; 21,72</t>
+          <t>7,88; 22,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,64; 24,7</t>
+          <t>11,33; 25,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 11,57</t>
+          <t>3,06; 11,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,99; 25,36</t>
+          <t>10,76; 25,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,06; 54,32</t>
+          <t>8,07; 56,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,52; 23,29</t>
+          <t>13,65; 23,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,61; 14,34</t>
+          <t>6,3; 14,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,08; 28,89</t>
+          <t>17,0; 28,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,94; 37,56</t>
+          <t>10,91; 38,21</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,58; 59,82</t>
+          <t>34,2; 58,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,36; 28,55</t>
+          <t>9,11; 27,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,42; 22,04</t>
+          <t>3,95; 20,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,07; 52,89</t>
+          <t>28,35; 52,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,28; 25,21</t>
+          <t>7,21; 24,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,44; 23,18</t>
+          <t>6,0; 23,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,01</t>
+          <t>0,0; 8,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,91; 51,4</t>
+          <t>33,82; 52,05</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,71; 22,78</t>
+          <t>10,67; 23,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,06; 18,48</t>
+          <t>6,6; 19,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>0,0; 4,07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,65; 32,75</t>
+          <t>15,79; 33,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,14; 26,48</t>
+          <t>9,39; 26,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,64; 18,48</t>
+          <t>4,56; 17,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,87; 26,11</t>
+          <t>9,87; 26,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,64; 31,94</t>
+          <t>15,19; 32,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,37; 28,04</t>
+          <t>10,44; 27,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,89; 18,49</t>
+          <t>4,76; 18,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,33; 26,85</t>
+          <t>11,88; 27,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,07; 29,39</t>
+          <t>17,16; 29,82</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,86; 23,95</t>
+          <t>11,75; 23,34</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,33; 16,22</t>
+          <t>5,9; 15,86</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,75; 23,94</t>
+          <t>13,37; 24,18</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,12; 32,48</t>
+          <t>19,74; 32,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,03; 28,75</t>
+          <t>16,49; 28,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,42; 27,79</t>
+          <t>16,71; 28,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,55; 23,96</t>
+          <t>11,32; 24,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,37; 37,86</t>
+          <t>25,29; 37,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,3; 25,76</t>
+          <t>14,7; 26,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,04; 25,1</t>
+          <t>14,14; 24,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,32; 15,54</t>
+          <t>6,29; 15,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>23,97; 33,02</t>
+          <t>23,94; 33,09</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,64; 24,8</t>
+          <t>16,88; 24,88</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,64; 24,45</t>
+          <t>16,98; 24,81</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,87; 17,4</t>
+          <t>9,93; 17,34</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,94; 31,08</t>
+          <t>19,28; 30,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,4; 30,02</t>
+          <t>19,1; 29,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,93; 31,54</t>
+          <t>20,91; 31,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,03; 15,62</t>
+          <t>6,93; 15,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,64; 28,92</t>
+          <t>18,48; 28,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,3; 19,1</t>
+          <t>10,12; 19,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,5; 23,76</t>
+          <t>14,32; 24,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,28; 11,63</t>
+          <t>4,45; 11,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,38; 28,03</t>
+          <t>20,65; 28,12</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16,03; 22,96</t>
+          <t>15,97; 22,88</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18,84; 26,07</t>
+          <t>18,83; 25,98</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,67; 12,09</t>
+          <t>6,5; 12,15</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22,8; 28,02</t>
+          <t>22,61; 27,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18,08; 22,89</t>
+          <t>17,9; 22,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19,51; 24,36</t>
+          <t>19,45; 24,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19,13; 35,05</t>
+          <t>18,92; 35,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,97; 26,0</t>
+          <t>20,94; 26,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,83; 18,31</t>
+          <t>13,63; 18,12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,58; 19,0</t>
+          <t>14,83; 19,22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15,33; 22,47</t>
+          <t>15,31; 22,34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22,42; 26,13</t>
+          <t>22,42; 26,17</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16,22; 19,69</t>
+          <t>16,49; 19,7</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17,64; 21,0</t>
+          <t>17,73; 21,07</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,87; 25,8</t>
+          <t>17,75; 25,91</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que no hacen ejercicio (tasa de respuesta: 99,44%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>10508</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15212</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8603</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>50425</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>13413</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>14071</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9538</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>54981</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>23921</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>29283</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>18141</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>105407</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>6185; 15324</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9604; 20431</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5370; 13900</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>43204; 58463</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>8655; 19688</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>9308; 20782</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5483; 15408</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>46844; 61756</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>17026; 30710</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>20915; 37215</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>11774; 25424</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>93703; 114510</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>22381</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19776</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>25394</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>45062</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>14322</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>19105</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>17466</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>16544</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>36703</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>38881</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>42859</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>61606</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>16171; 30093</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14128; 26725</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>18853; 32167</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>20433; 83171</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>9097; 20754</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>12912; 26269</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>12550; 24522</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>10595; 24847</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>28712; 45026</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>30374; 49461</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>34297; 52001</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>35521; 122468</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>20483</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11366</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16082</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6765</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>14418</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10971</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>12947</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>7256</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>34901</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>22337</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>29028</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>14022</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>14664; 26473</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7242; 17644</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11007; 22816</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3513; 11334</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9940; 19713</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6831; 16652</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8175; 18479</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>4155; 11850</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>26057; 43631</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>15588; 30282</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>21697; 37177</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>9393; 20012</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>14224</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10463</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21415</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>13830</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5069</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>14056</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>17842</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>28054</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>15532</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>35470</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>27830</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>9368; 20704</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>6487; 15857</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>15348; 28673</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>5529; 15739</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>8962; 20273</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2471; 9619</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>8737; 20365</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>6306; 44527</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>21016; 36489</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>9924; 22449</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>26880; 44974</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>16181; 56655</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>19204</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7515</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4744</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>18129</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>6905</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5841</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>37333</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>14420</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>10585</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>14315; 24428</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4000; 12262</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1715; 8796</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>12712; 23548</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3373; 11472</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2781; 10739</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3521</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>29323; 45127</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>9671; 21320</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5928; 17133</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3061</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>12852</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8837</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5642</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7840</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>13910</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>10624</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5734</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>10629</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>26761</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>19461</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>11376</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>18469</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>8853; 19017</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>5117; 14316</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2474; 9520</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>4557; 12108</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>9071; 19282</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>5997; 16056</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2750; 10878</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>6673; 15528</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>19868; 34532</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>13155; 26133</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>6604; 17768</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>13684; 24745</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>33002</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>30698</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>30131</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>21071</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>42129</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>27822</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>26878</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>15573</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>75131</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>58520</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>57009</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>36644</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>25393; 41358</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>22762; 38831</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>22726; 38351</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>13963; 29872</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>34145; 51227</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>20998; 37694</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>20091; 35051</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>9732; 23641</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>63121; 87245</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>47401; 69884</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>47223; 69021</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>27602; 48220</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>39077</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>39584</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>42356</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>14244</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>38722</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>23878</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>31945</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>11924</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>77799</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>63461</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>74301</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>26169</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>30450; 47509</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>31339; 48253</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>34334; 51460</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>9125; 19901</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>30194; 46976</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>17211; 32376</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>24371; 41524</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>6970; 18399</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>66354; 90351</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>53365; 76460</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>62973; 86871</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>18761; 35053</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>171730</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>143451</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>154366</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>155395</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>168873</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>118446</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>124404</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>135501</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>340603</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>261896</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>278770</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>290896</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>153497; 189808</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>126335; 161135</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>136754; 171778</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>125608; 237866</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>151063; 188270</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>101268; 134647</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>109816; 142331</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>116013; 169253</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>313924; 366474</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>238919; 285448</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>255880; 304123</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>252371; 368345</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP24_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,77; 29,15</t>
+          <t>13,1; 30,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,01; 36,19</t>
+          <t>18,52; 39,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,36; 24,23</t>
+          <t>8,55; 23,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58,96; 79,78</t>
+          <t>59,18; 79,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,37; 32,69</t>
+          <t>14,24; 31,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,69; 32,8</t>
+          <t>14,41; 32,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,65; 24,3</t>
+          <t>8,61; 23,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>59,02; 77,81</t>
+          <t>59,85; 78,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,1; 27,23</t>
+          <t>15,43; 28,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,46; 31,06</t>
+          <t>17,61; 31,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,75; 21,05</t>
+          <t>10,29; 21,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>61,38; 75,02</t>
+          <t>61,64; 75,99</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,02; 29,82</t>
+          <t>16,65; 29,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,61; 25,74</t>
+          <t>13,27; 25,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,14; 30,95</t>
+          <t>18,43; 31,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,16; 65,77</t>
+          <t>15,91; 66,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,36; 19,08</t>
+          <t>8,9; 18,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,68; 23,77</t>
+          <t>12,04; 24,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,45; 22,38</t>
+          <t>11,0; 22,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,5; 19,93</t>
+          <t>8,38; 20,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,69; 21,47</t>
+          <t>13,57; 22,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,17; 23,07</t>
+          <t>14,3; 22,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,06; 24,35</t>
+          <t>15,87; 24,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,15; 48,77</t>
+          <t>14,12; 48,72</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,17; 40,02</t>
+          <t>21,13; 41,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,62; 25,88</t>
+          <t>10,39; 25,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,47; 34,14</t>
+          <t>16,19; 34,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 19,45</t>
+          <t>6,24; 19,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,13; 28,03</t>
+          <t>13,42; 28,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,59; 23,37</t>
+          <t>9,6; 23,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,69; 26,43</t>
+          <t>11,47; 25,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,19; 17,64</t>
+          <t>6,0; 17,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,09; 31,97</t>
+          <t>19,99; 32,22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,18; 21,72</t>
+          <t>11,21; 21,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,87; 27,19</t>
+          <t>15,53; 26,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 15,95</t>
+          <t>7,43; 15,95</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,51; 27,66</t>
+          <t>11,35; 27,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,46; 20,67</t>
+          <t>7,84; 20,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,94; 37,26</t>
+          <t>19,59; 37,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,88; 22,44</t>
+          <t>7,98; 22,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,33; 25,63</t>
+          <t>11,61; 25,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 11,91</t>
+          <t>2,8; 10,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,76; 25,08</t>
+          <t>11,02; 26,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,07; 56,99</t>
+          <t>8,49; 55,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,65; 23,7</t>
+          <t>13,65; 23,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 14,25</t>
+          <t>6,46; 14,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,0; 28,44</t>
+          <t>17,45; 28,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,91; 38,21</t>
+          <t>10,96; 42,3</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,2; 58,37</t>
+          <t>33,66; 58,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,11; 27,93</t>
+          <t>9,16; 28,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 20,25</t>
+          <t>4,29; 21,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,42 +1297,42 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,35; 52,51</t>
+          <t>28,22; 52,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,21; 24,54</t>
+          <t>7,35; 24,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,0; 23,17</t>
+          <t>6,4; 23,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,65</t>
+          <t>0,0; 6,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,82; 52,05</t>
+          <t>35,05; 52,07</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,67; 23,52</t>
+          <t>9,82; 23,18</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,6; 19,08</t>
+          <t>6,73; 18,4</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,07</t>
+          <t>0,0; 5,0</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,79; 33,93</t>
+          <t>14,45; 32,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,39; 26,26</t>
+          <t>8,93; 24,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,56; 17,54</t>
+          <t>4,84; 18,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,87; 26,23</t>
+          <t>10,18; 26,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,19; 32,28</t>
+          <t>15,57; 32,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,44; 27,94</t>
+          <t>11,2; 29,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,76; 18,84</t>
+          <t>4,91; 19,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,88; 27,64</t>
+          <t>12,26; 28,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,16; 29,82</t>
+          <t>17,45; 29,96</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,75; 23,34</t>
+          <t>12,21; 24,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,9; 15,86</t>
+          <t>6,09; 15,5</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,37; 24,18</t>
+          <t>13,36; 24,41</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,74; 32,15</t>
+          <t>19,76; 33,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,49; 28,13</t>
+          <t>17,08; 28,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,71; 28,2</t>
+          <t>16,83; 28,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,32; 24,21</t>
+          <t>11,9; 24,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,29; 37,94</t>
+          <t>25,07; 37,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,7; 26,4</t>
+          <t>14,34; 25,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,14; 24,66</t>
+          <t>13,75; 24,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,29; 15,28</t>
+          <t>6,59; 15,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>23,94; 33,09</t>
+          <t>24,1; 33,72</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,88; 24,88</t>
+          <t>16,97; 25,3</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,98; 24,81</t>
+          <t>16,67; 24,37</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,93; 17,34</t>
+          <t>9,69; 17,57</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,28; 30,09</t>
+          <t>19,59; 30,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,1; 29,41</t>
+          <t>19,34; 30,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,91; 31,34</t>
+          <t>20,89; 31,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,93; 15,12</t>
+          <t>7,17; 15,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,48; 28,76</t>
+          <t>18,77; 29,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,12; 19,04</t>
+          <t>10,16; 18,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,32; 24,39</t>
+          <t>14,25; 23,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,45; 11,73</t>
+          <t>4,65; 11,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,65; 28,12</t>
+          <t>20,66; 28,38</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15,97; 22,88</t>
+          <t>15,61; 22,62</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18,83; 25,98</t>
+          <t>18,63; 26,2</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,5; 12,15</t>
+          <t>6,55; 11,89</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22,61; 27,96</t>
+          <t>22,76; 27,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,9; 22,83</t>
+          <t>17,86; 22,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19,45; 24,43</t>
+          <t>19,44; 24,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18,92; 35,83</t>
+          <t>18,78; 34,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,94; 26,1</t>
+          <t>20,85; 25,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,63; 18,12</t>
+          <t>13,65; 18,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,83; 19,22</t>
+          <t>14,58; 18,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15,31; 22,34</t>
+          <t>15,28; 22,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22,42; 26,17</t>
+          <t>22,45; 26,16</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16,49; 19,7</t>
+          <t>16,42; 19,62</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17,73; 21,07</t>
+          <t>17,7; 20,96</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,75; 25,91</t>
+          <t>17,68; 25,51</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6185; 15324</t>
+          <t>6886; 15852</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9604; 20431</t>
+          <t>10456; 22223</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5370; 13900</t>
+          <t>4903; 13312</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43204; 58463</t>
+          <t>43369; 58159</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8655; 19688</t>
+          <t>8576; 19127</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9308; 20782</t>
+          <t>9133; 20527</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5483; 15408</t>
+          <t>5457; 14929</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46844; 61756</t>
+          <t>47503; 62020</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17026; 30710</t>
+          <t>17402; 31666</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20915; 37215</t>
+          <t>21101; 37200</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11774; 25424</t>
+          <t>12426; 25474</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>93703; 114510</t>
+          <t>94096; 116003</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16171; 30093</t>
+          <t>16806; 29679</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14128; 26725</t>
+          <t>13775; 26565</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18853; 32167</t>
+          <t>19162; 33253</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20433; 83171</t>
+          <t>20119; 83955</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9097; 20754</t>
+          <t>9682; 20039</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12912; 26269</t>
+          <t>13306; 26959</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12550; 24522</t>
+          <t>12050; 24565</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10595; 24847</t>
+          <t>10442; 24987</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28712; 45026</t>
+          <t>28449; 46296</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30374; 49461</t>
+          <t>30651; 49264</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34297; 52001</t>
+          <t>33896; 53253</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35521; 122468</t>
+          <t>35451; 122329</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14664; 26473</t>
+          <t>13979; 27159</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7242; 17644</t>
+          <t>7085; 17327</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11007; 22816</t>
+          <t>10822; 22864</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3513; 11334</t>
+          <t>3635; 11230</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9940; 19713</t>
+          <t>9441; 20063</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6831; 16652</t>
+          <t>6842; 16974</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8175; 18479</t>
+          <t>8015; 17929</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4155; 11850</t>
+          <t>4030; 11568</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26057; 43631</t>
+          <t>27283; 43977</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15588; 30282</t>
+          <t>15624; 29667</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21697; 37177</t>
+          <t>21232; 36782</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9393; 20012</t>
+          <t>9321; 20012</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9368; 20704</t>
+          <t>8494; 20380</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6487; 15857</t>
+          <t>6014; 15571</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15348; 28673</t>
+          <t>15075; 28960</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5529; 15739</t>
+          <t>5597; 15428</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8962; 20273</t>
+          <t>9188; 20050</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2471; 9619</t>
+          <t>2262; 8797</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8737; 20365</t>
+          <t>8947; 21172</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6306; 44527</t>
+          <t>6632; 43285</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21016; 36489</t>
+          <t>21011; 36195</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9924; 22449</t>
+          <t>10180; 22609</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26880; 44974</t>
+          <t>27593; 45170</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16181; 56655</t>
+          <t>16252; 62721</t>
         </is>
       </c>
     </row>
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14315; 24428</t>
+          <t>14086; 24314</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4000; 12262</t>
+          <t>4020; 12522</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1715; 8796</t>
+          <t>1862; 9133</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3061,42 +3061,42 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12712; 23548</t>
+          <t>12657; 23394</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3373; 11472</t>
+          <t>3436; 11499</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2781; 10739</t>
+          <t>2964; 10677</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3521</t>
+          <t>0; 2844</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29323; 45127</t>
+          <t>30388; 45144</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9671; 21320</t>
+          <t>8903; 21018</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5928; 17133</t>
+          <t>6046; 16523</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3061</t>
+          <t>0; 3761</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8853; 19017</t>
+          <t>8099; 18409</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5117; 14316</t>
+          <t>4869; 13376</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2474; 9520</t>
+          <t>2629; 9830</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4557; 12108</t>
+          <t>4701; 12170</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9071; 19282</t>
+          <t>9302; 19367</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5997; 16056</t>
+          <t>6438; 16724</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2750; 10878</t>
+          <t>2832; 11309</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6673; 15528</t>
+          <t>6886; 15781</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19868; 34532</t>
+          <t>20205; 34691</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13155; 26133</t>
+          <t>13673; 27334</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6604; 17768</t>
+          <t>6817; 17360</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13684; 24745</t>
+          <t>13679; 24988</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>25393; 41358</t>
+          <t>25413; 42570</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>22762; 38831</t>
+          <t>23575; 39259</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22726; 38351</t>
+          <t>22898; 38590</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13963; 29872</t>
+          <t>14678; 29808</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>34145; 51227</t>
+          <t>33850; 51140</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20998; 37694</t>
+          <t>20483; 36250</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20091; 35051</t>
+          <t>19536; 34693</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9732; 23641</t>
+          <t>10196; 23239</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>63121; 87245</t>
+          <t>63543; 88883</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>47401; 69884</t>
+          <t>47646; 71043</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>47223; 69021</t>
+          <t>46373; 67791</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>27602; 48220</t>
+          <t>26942; 48853</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>30450; 47509</t>
+          <t>30933; 48752</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>31339; 48253</t>
+          <t>31735; 49672</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>34334; 51460</t>
+          <t>34289; 51306</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9125; 19901</t>
+          <t>9436; 20758</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>30194; 46976</t>
+          <t>30659; 47570</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17211; 32376</t>
+          <t>17277; 32250</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24371; 41524</t>
+          <t>24257; 40661</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6970; 18399</t>
+          <t>7291; 18497</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>66354; 90351</t>
+          <t>66386; 91175</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>53365; 76460</t>
+          <t>52160; 75580</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>62973; 86871</t>
+          <t>62311; 87612</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>18761; 35053</t>
+          <t>18901; 34293</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>153497; 189808</t>
+          <t>154519; 189953</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>126335; 161135</t>
+          <t>126031; 160032</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>136754; 171778</t>
+          <t>136692; 172716</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>125608; 237866</t>
+          <t>124635; 229313</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>151063; 188270</t>
+          <t>150375; 187450</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>101268; 134647</t>
+          <t>101381; 136456</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>109816; 142331</t>
+          <t>108004; 139898</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>116013; 169253</t>
+          <t>115769; 168429</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>313924; 366474</t>
+          <t>314300; 366319</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>238919; 285448</t>
+          <t>237913; 284186</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>255880; 304123</t>
+          <t>255509; 302504</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>252371; 368345</t>
+          <t>251372; 362673</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP24_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22,27%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22,21%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15,04%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>67,27%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>19,99%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>26,94%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>15,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>68,81%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22,27%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22,21%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,04%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,1; 30,16</t>
+          <t>14,2; 31,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,52; 39,36</t>
+          <t>14,2; 31,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,55; 23,2</t>
+          <t>8,53; 23,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59,18; 79,36</t>
+          <t>57,0; 76,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,24; 31,76</t>
+          <t>12,46; 30,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,41; 32,4</t>
+          <t>17,39; 37,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,61; 23,54</t>
+          <t>8,72; 22,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>59,85; 78,14</t>
+          <t>52,49; 71,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,43; 28,08</t>
+          <t>15,17; 27,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,61; 31,05</t>
+          <t>18,36; 32,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,29; 21,09</t>
+          <t>10,28; 21,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>61,64; 75,99</t>
+          <t>57,38; 71,04</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13,17%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17,29%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15,94%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12,81%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>22,17%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>19,05%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>24,43%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>35,63%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>17,29%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,94%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,65; 29,41</t>
+          <t>8,51; 18,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,27; 25,58</t>
+          <t>11,62; 24,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,43; 31,99</t>
+          <t>10,9; 21,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,91; 66,39</t>
+          <t>7,86; 19,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,9; 18,43</t>
+          <t>15,54; 28,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,04; 24,39</t>
+          <t>13,53; 26,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,0; 22,42</t>
+          <t>18,62; 31,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,38; 20,05</t>
+          <t>14,22; 29,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,57; 22,08</t>
+          <t>13,7; 21,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,3; 22,98</t>
+          <t>14,07; 22,59</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,87; 24,94</t>
+          <t>15,71; 24,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,12; 48,72</t>
+          <t>11,92; 21,66</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20,5%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15,4%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18,52%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>30,97%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>16,67%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>24,06%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11,61%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20,5%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18,52%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,13; 41,06</t>
+          <t>14,21; 29,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,39; 25,41</t>
+          <t>9,51; 23,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,19; 34,21</t>
+          <t>11,56; 26,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,24; 19,27</t>
+          <t>5,33; 16,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,42; 28,53</t>
+          <t>22,13; 41,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,6; 23,82</t>
+          <t>9,93; 24,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,47; 25,65</t>
+          <t>16,13; 34,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 17,22</t>
+          <t>5,66; 18,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,99; 32,22</t>
+          <t>20,12; 32,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,21; 21,28</t>
+          <t>11,57; 22,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,53; 26,9</t>
+          <t>16,12; 27,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,43; 15,95</t>
+          <t>6,79; 15,3</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17,48%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>17,31%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20,85%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>19,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>13,64%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>27,83%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14,24%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17,48%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,31%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,35; 27,22</t>
+          <t>11,64; 24,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,84; 20,3</t>
+          <t>2,97; 11,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,59; 37,63</t>
+          <t>10,99; 25,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,98; 22,0</t>
+          <t>7,72; 49,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,61; 25,34</t>
+          <t>11,64; 26,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 10,89</t>
+          <t>8,35; 21,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,02; 26,08</t>
+          <t>19,54; 37,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,49; 55,4</t>
+          <t>7,61; 21,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,65; 23,51</t>
+          <t>13,52; 23,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,46; 14,36</t>
+          <t>6,61; 14,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,45; 28,56</t>
+          <t>17,08; 28,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,96; 42,3</t>
+          <t>10,56; 32,79</t>
         </is>
       </c>
     </row>
@@ -1209,44 +1209,44 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>40,43%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14,77%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12,6%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>45,88%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>17,12%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>10,92%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>40,43%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>14,77%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>12,6%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
           <t>43,06%</t>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>33,66; 58,1</t>
+          <t>28,07; 52,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,16; 28,52</t>
+          <t>7,28; 25,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,29; 21,03</t>
+          <t>5,44; 23,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 8,4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>34,58; 59,82</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,36; 28,55</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,42; 22,04</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>28,22; 52,17</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,35; 24,6</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,4; 23,04</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,99</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35,05; 52,07</t>
+          <t>33,91; 51,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,82; 23,18</t>
+          <t>9,71; 22,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,73; 18,4</t>
+          <t>7,06; 18,48</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,0</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>23,29%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18,49%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9,93%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17,05%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>22,93%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>16,21%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>10,4%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>16,98%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>23,29%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>18,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9,93%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,45; 32,84</t>
+          <t>15,64; 31,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,93; 24,54</t>
+          <t>10,37; 28,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,84; 18,11</t>
+          <t>4,89; 18,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,18; 26,36</t>
+          <t>10,89; 25,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,57; 32,42</t>
+          <t>14,65; 32,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,2; 29,1</t>
+          <t>9,14; 26,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,91; 19,59</t>
+          <t>4,64; 18,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,26; 28,09</t>
+          <t>8,56; 23,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,45; 29,96</t>
+          <t>17,07; 29,39</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,21; 24,41</t>
+          <t>11,86; 23,95</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,09; 15,5</t>
+          <t>6,33; 16,22</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,36; 24,41</t>
+          <t>11,23; 21,56</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>31,21%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19,48%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18,91%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10,99%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>25,66%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>22,24%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>22,15%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17,08%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>31,21%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19,48%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>18,91%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,76; 33,1</t>
+          <t>25,37; 37,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,08; 28,44</t>
+          <t>14,3; 25,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,83; 28,37</t>
+          <t>14,04; 25,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,9; 24,16</t>
+          <t>6,87; 16,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,07; 37,88</t>
+          <t>20,12; 32,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,34; 25,39</t>
+          <t>17,03; 28,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,75; 24,41</t>
+          <t>16,42; 27,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,59; 15,02</t>
+          <t>11,78; 22,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>24,1; 33,72</t>
+          <t>23,97; 33,02</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,97; 25,3</t>
+          <t>16,64; 24,8</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,67; 24,37</t>
+          <t>16,64; 24,45</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,69; 17,57</t>
+          <t>10,39; 17,52</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>23,7%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>14,04%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>18,76%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7,59%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>24,75%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>24,12%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>25,8%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>10,82%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>23,7%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>18,76%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,59; 30,87</t>
+          <t>18,64; 28,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,34; 30,27</t>
+          <t>10,3; 19,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,89; 31,25</t>
+          <t>14,5; 23,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,17; 15,77</t>
+          <t>4,34; 11,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,77; 29,12</t>
+          <t>18,94; 31,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,16; 18,97</t>
+          <t>19,4; 30,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,25; 23,88</t>
+          <t>20,93; 31,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,65; 11,8</t>
+          <t>6,31; 14,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,66; 28,38</t>
+          <t>20,38; 28,03</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15,61; 22,62</t>
+          <t>16,03; 22,96</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18,63; 26,2</t>
+          <t>18,84; 26,07</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,55; 11,89</t>
+          <t>6,33; 11,67</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>23,41%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>15,94%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>16,8%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>25,29%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>20,33%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>21,96%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>23,41%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>23,41%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>15,94%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22,76; 27,98</t>
+          <t>20,97; 26,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,86; 22,68</t>
+          <t>13,83; 18,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19,44; 24,57</t>
+          <t>14,58; 19,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18,78; 34,54</t>
+          <t>14,19; 20,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,85; 25,99</t>
+          <t>22,8; 28,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,65; 18,37</t>
+          <t>18,08; 22,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,58; 18,89</t>
+          <t>19,51; 24,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15,28; 22,23</t>
+          <t>15,46; 20,49</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22,45; 26,16</t>
+          <t>22,42; 26,13</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16,42; 19,62</t>
+          <t>16,22; 19,69</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17,7; 20,96</t>
+          <t>17,64; 21,0</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,68; 25,51</t>
+          <t>15,43; 19,39</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>60</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13413</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14071</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9538</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>43148</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>10508</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>15212</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>8603</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>50425</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>13413</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>14071</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9538</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54981</t>
+          <t>34912</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>105407</t>
+          <t>78060</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6886; 15852</t>
+          <t>8551; 19232</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10456; 22223</t>
+          <t>9000; 19852</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4903; 13312</t>
+          <t>5411; 15150</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43369; 58159</t>
+          <t>36562; 49166</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8576; 19127</t>
+          <t>6550; 16139</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9133; 20527</t>
+          <t>9820; 21019</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5457; 14929</t>
+          <t>5001; 13179</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47503; 62020</t>
+          <t>29645; 40471</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17402; 31666</t>
+          <t>17104; 30540</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21101; 37200</t>
+          <t>22004; 38767</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12426; 25474</t>
+          <t>12419; 25585</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>94096; 116003</t>
+          <t>69210; 85697</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14322</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19105</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17466</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14538</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>22381</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>19776</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>25394</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>45062</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14322</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19105</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>17466</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>20331</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>34869</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16806; 29679</t>
+          <t>9259; 19796</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13775; 26565</t>
+          <t>12845; 27128</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19162; 33253</t>
+          <t>11941; 23997</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20119; 83955</t>
+          <t>8919; 22589</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9682; 20039</t>
+          <t>15682; 28755</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13306; 26959</t>
+          <t>14044; 27401</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12050; 24565</t>
+          <t>19350; 32664</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10442; 24987</t>
+          <t>14247; 30054</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28449; 46296</t>
+          <t>28721; 45207</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30651; 49264</t>
+          <t>30155; 48415</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33896; 53253</t>
+          <t>33548; 53299</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35451; 122329</t>
+          <t>25470; 46299</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>14418</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10971</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12947</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5912</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>20483</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>11366</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>16082</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6765</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>14418</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>10971</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>12947</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>6157</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14022</t>
+          <t>12069</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13979; 27159</t>
+          <t>9990; 20593</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7085; 17327</t>
+          <t>6776; 16524</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10822; 22864</t>
+          <t>8083; 18299</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3635; 11230</t>
+          <t>3163; 9832</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9441; 20063</t>
+          <t>14635; 27668</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6842; 16974</t>
+          <t>6773; 16855</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8015; 17929</t>
+          <t>10777; 22949</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4030; 11568</t>
+          <t>3202; 10432</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27283; 43977</t>
+          <t>27452; 43758</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15624; 29667</t>
+          <t>16138; 30794</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21232; 36782</t>
+          <t>22037; 37395</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9321; 20012</t>
+          <t>7876; 17742</t>
         </is>
       </c>
     </row>
@@ -2702,37 +2702,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>13830</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5069</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14056</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15043</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>14224</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>10463</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>21415</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9987</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>13830</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5069</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14056</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17842</t>
+          <t>9882</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27830</t>
+          <t>24924</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8494; 20380</t>
+          <t>9211; 19537</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6014; 15571</t>
+          <t>2395; 9342</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15075; 28960</t>
+          <t>8923; 20592</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5597; 15428</t>
+          <t>5568; 35969</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9188; 20050</t>
+          <t>8717; 20068</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2262; 8797</t>
+          <t>6404; 16255</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8947; 21172</t>
+          <t>15039; 28624</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6632; 43285</t>
+          <t>5394; 15276</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21011; 36195</t>
+          <t>20812; 35862</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10180; 22609</t>
+          <t>10411; 22579</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27593; 45170</t>
+          <t>27018; 45682</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16252; 62721</t>
+          <t>15096; 46895</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,44 +2973,44 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>18129</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6905</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5841</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>19204</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>7515</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>4744</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>18129</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>6905</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>5841</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>751</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
           <t>37333</t>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>866</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14086; 24314</t>
+          <t>12586; 23717</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4020; 12522</t>
+          <t>3404; 11786</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1862; 9133</t>
+          <t>2523; 10746</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>0; 3325</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>14473; 25037</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4109; 12532</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1920; 9575</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>12657; 23394</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3436; 11499</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>2964; 10677</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0; 2844</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>30388; 45144</t>
+          <t>29394; 44559</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8903; 21018</t>
+          <t>8805; 20648</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6046; 16523</t>
+          <t>6339; 16595</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3761</t>
+          <t>0; 3162</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>13910</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10624</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5734</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8344</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>12852</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>8837</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>5642</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7840</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>13910</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>10624</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5734</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>18469</t>
+          <t>15111</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8099; 18409</t>
+          <t>9343; 19076</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4869; 13376</t>
+          <t>5958; 16116</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2629; 9830</t>
+          <t>2824; 10679</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4701; 12170</t>
+          <t>5330; 12269</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9302; 19367</t>
+          <t>8214; 18355</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6438; 16724</t>
+          <t>4984; 14437</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2832; 11309</t>
+          <t>2519; 10028</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6886; 15781</t>
+          <t>3918; 10801</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20205; 34691</t>
+          <t>19770; 34032</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13673; 27334</t>
+          <t>13282; 26821</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6817; 17360</t>
+          <t>7094; 18169</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13679; 24988</t>
+          <t>10631; 20416</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>42129</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>27822</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>26878</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>15391</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>33002</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>30698</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>30131</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>21071</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>42129</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>27822</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>26878</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>15573</t>
+          <t>20145</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>36644</t>
+          <t>35535</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>25413; 42570</t>
+          <t>34253; 51113</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>23575; 39259</t>
+          <t>20424; 36788</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22898; 38590</t>
+          <t>19951; 35671</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14678; 29808</t>
+          <t>9625; 22837</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>33850; 51140</t>
+          <t>25880; 41775</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20483; 36250</t>
+          <t>23508; 39683</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19536; 34693</t>
+          <t>22335; 37793</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>10196; 23239</t>
+          <t>14321; 27722</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>63543; 88883</t>
+          <t>63186; 87042</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>47646; 71043</t>
+          <t>46736; 69660</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46373; 67791</t>
+          <t>46286; 68020</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>26942; 48853</t>
+          <t>27191; 45838</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>38722</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>23878</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>31945</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>39077</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>39584</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>42356</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>14244</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>38722</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>23878</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>31945</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>11924</t>
+          <t>13893</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>26169</t>
+          <t>25996</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>30933; 48752</t>
+          <t>30445; 47240</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>31735; 49672</t>
+          <t>17515; 32471</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>34289; 51306</t>
+          <t>24686; 40454</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9436; 20758</t>
+          <t>6922; 18912</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>30659; 47570</t>
+          <t>29905; 49075</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17277; 32250</t>
+          <t>31843; 49268</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24257; 40661</t>
+          <t>34357; 51782</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7291; 18497</t>
+          <t>8860; 20779</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>66386; 91175</t>
+          <t>65475; 90040</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>52160; 75580</t>
+          <t>53547; 76717</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>62311; 87612</t>
+          <t>63000; 87168</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>18901; 34293</t>
+          <t>18971; 35011</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>260</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>237</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>185</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>168873</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>118446</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>124404</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>115344</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>171730</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>143451</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>154366</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>155395</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>168873</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>118446</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>124404</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>135501</t>
+          <t>112087</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>290896</t>
+          <t>227431</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>154519; 189953</t>
+          <t>151269; 187574</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>126031; 160032</t>
+          <t>102726; 136006</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>136692; 172716</t>
+          <t>107953; 140703</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>124635; 229313</t>
+          <t>98906; 144738</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>150375; 187450</t>
+          <t>154794; 190240</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>101381; 136456</t>
+          <t>127592; 161534</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>108004; 139898</t>
+          <t>137167; 171263</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>115769; 168429</t>
+          <t>97037; 128550</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>314300; 366319</t>
+          <t>313929; 365840</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>237913; 284186</t>
+          <t>235037; 285202</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>255509; 302504</t>
+          <t>254577; 303220</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>251372; 362673</t>
+          <t>204352; 256861</t>
         </is>
       </c>
     </row>
